--- a/cuadros/JUNIO/BOSQUE.xlsx
+++ b/cuadros/JUNIO/BOSQUE.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,6 +625,76 @@
       <c r="N3" t="inlineStr">
         <is>
           <t>ID_20260601163324</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BOSQUE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AGROPECUARIA LATIN FRUITS C.A.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>006896</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SUB VICTOR J. SALCEDO</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>RESPONSABLE INGRESA SKU DE OCUMO CHINO A DESTIEMPO</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>INC_170549_0.png INC_170549_1.png INC_170549_2.png</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>ID_20260602170549</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/BOSQUE.xlsx
+++ b/cuadros/JUNIO/BOSQUE.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor rgb="FF00B0F0"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -695,6 +702,76 @@
       <c r="N4" t="inlineStr">
         <is>
           <t>ID_20260602170549</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BOSQUE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LA CARIDAD C.A.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>00471406</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SUB SUGGEY D. CASTRO</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>OTRAS.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>SE RECIBEN 1504.10KG DE POLLO ENTERO CONGELADO, EN FACTURA 1499.30KG. DIFERENCIA: 4.8KG EXCEDENTE</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>EXCEDENTES</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>INC_065935_0.png INC_065935_1.png INC_065935_2.png INC_065935_3.png INC_065935_4.png</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>ID_20260603065936</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/BOSQUE.xlsx
+++ b/cuadros/JUNIO/BOSQUE.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -57,7 +56,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -421,7 +420,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6"/>
+  <cols>
+    <col width="46.07421875" customWidth="1" min="14" max="14"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -486,12 +488,12 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>FOTO_INCIDENCIA</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ID</t>
         </is>
       </c>
     </row>
@@ -556,12 +558,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>ID_20260601161800</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>INC_161800_0.png INC_161800_1.png</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>ID_20260601161800</t>
         </is>
       </c>
     </row>
@@ -626,12 +628,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>ID_20260601163324</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>INC_163324_0.png INC_163324_1.png</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>ID_20260601163324</t>
         </is>
       </c>
     </row>
@@ -696,12 +698,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>ID_20260602170549</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>INC_170549_0.png INC_170549_1.png INC_170549_2.png</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>ID_20260602170549</t>
         </is>
       </c>
     </row>
@@ -766,12 +768,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>ID_20260603065936</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>INC_065935_0.png INC_065935_1.png INC_065935_2.png INC_065935_3.png INC_065935_4.png</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>ID_20260603065936</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/BOSQUE.xlsx
+++ b/cuadros/JUNIO/BOSQUE.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -56,7 +57,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -419,11 +420,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6"/>
-  <cols>
-    <col width="46.07421875" customWidth="1" min="14" max="14"/>
-  </cols>
+  <dimension ref="A1:N6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -743,11 +741,6 @@
           <t>OTRAS.</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>SE RECIBEN 1504.10KG DE POLLO ENTERO CONGELADO, EN FACTURA 1499.30KG. DIFERENCIA: 4.8KG EXCEDENTE</t>
@@ -774,6 +767,71 @@
       <c r="N5" t="inlineStr">
         <is>
           <t>INC_065935_0.png INC_065935_1.png INC_065935_2.png INC_065935_3.png INC_065935_4.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BOSQUE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>WAYNE CORP, C.A</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>020064</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SUB VIRGILIO A. ARAUJO</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>RECEPCIÓN SIN AUTORIZACIÓN DE CMF.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>TIPO E</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>RESPONSABLE INICIA RECEPCIÓN SIN AUTORIZACIÓN PREVIA</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ID_20260603144429</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/BOSQUE.xlsx
+++ b/cuadros/JUNIO/BOSQUE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -832,6 +832,76 @@
       <c r="M6" t="inlineStr">
         <is>
           <t>ID_20260603144429</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BOSQUE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AGROPECUARIA ORO BLANCO, C.A.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>36868</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DEVOLUCION</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SPCP NELSON P. RUIZ</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>RESPONSABLE INGRESA NÚMERO DE DOCUMENTO INCORRECTO</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ID_20260603150755</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>INC_150755_0.png INC_150755_1.png</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/BOSQUE.xlsx
+++ b/cuadros/JUNIO/BOSQUE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -902,6 +902,71 @@
       <c r="N7" t="inlineStr">
         <is>
           <t>INC_150755_0.png INC_150755_1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BOSQUE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AGROPECUARIA PUNTA LARGA, C.A.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>003175</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SUB MARIANGEL G. NOGUERA</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>RECEPCIÓN SIN AUTORIZACIÓN DE CMF.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>TIPO E</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>RESPONSABLE INICIA RECEPCIÓN SIN AUTORIZACIÓN PREVIA</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ID_20260605090644</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/BOSQUE.xlsx
+++ b/cuadros/JUNIO/BOSQUE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -967,6 +967,76 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>ID_20260605090644</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BOSQUE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CAVA LUXOR</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7256</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SUB VICTOR J. SALCEDO</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESPONSABLE NO CULMINA PROCESO DE RECEPCIÓN </t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ID_20260606090021</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>INC_090021_0.png</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/BOSQUE.xlsx
+++ b/cuadros/JUNIO/BOSQUE.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -37,6 +37,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
         <bgColor rgb="FF00B0F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
       </patternFill>
     </fill>
   </fills>
@@ -52,9 +58,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1037,6 +1044,76 @@
       <c r="N9" t="inlineStr">
         <is>
           <t>INC_090021_0.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BOSQUE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PRODUCTOS FRESCOS PROFRESCA, C.A.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>000028646</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>RECIBIDOR YONATIL HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>TIPO D</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SE RECIBEN 13 UNDS DE FLORETES DE BROCOLI, EN FACTURA 15 UNDS. DIFERENCIA: 02 UNDS FALTANTES.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>COBRO</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ID_20260606104533</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>INC_104533_0.png INC_104533_1.png INC_104533_2.png</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/BOSQUE.xlsx
+++ b/cuadros/JUNIO/BOSQUE.xlsx
@@ -1094,11 +1094,11 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0</v>
+        <v>7.44</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>SIN_FOTO</t>
+          <t>COB_114844_0.jpeg</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">

--- a/cuadros/JUNIO/BOSQUE.xlsx
+++ b/cuadros/JUNIO/BOSQUE.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1114,6 +1114,76 @@
       <c r="N10" t="inlineStr">
         <is>
           <t>INC_104533_0.png INC_104533_1.png INC_104533_2.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BOSQUE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GRUPO MADIOR 2023,C.A</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>37754</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>DEVOLUCION</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SPCP FREDYS JOSE LUGO RIERA</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESPONSABLE NO CULMINÓ A TIEMPO PROCESO DE FISCALIZACIÓN </t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ID_20260608074657</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>INC_074657_0.png</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/BOSQUE.xlsx
+++ b/cuadros/JUNIO/BOSQUE.xlsx
@@ -26,24 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor rgb="FF00B0F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,10 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -748,12 +734,13 @@
           <t>OTRAS.</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>SE RECIBEN 1504.10KG DE POLLO ENTERO CONGELADO, EN FACTURA 1499.30KG. DIFERENCIA: 4.8KG EXCEDENTE</t>
         </is>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" t="n">
         <v>15.31</v>
       </c>
       <c r="K5" t="inlineStr">
@@ -841,6 +828,7 @@
           <t>ID_20260603144429</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -976,6 +964,7 @@
           <t>ID_20260605090644</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1093,7 +1082,7 @@
           <t>SE RECIBEN 13 UNDS DE FLORETES DE BROCOLI, EN FACTURA 15 UNDS. DIFERENCIA: 02 UNDS FALTANTES.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="J10" t="n">
         <v>7.44</v>
       </c>
       <c r="K10" t="inlineStr">
@@ -1135,7 +1124,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1160,7 +1149,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESPONSABLE NO CULMINÓ A TIEMPO PROCESO DE FISCALIZACIÓN </t>
+          <t>RESPONSABLE NO CULMINÓ PROCESO DE FISCALIZACIÓN</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1178,12 +1167,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>ID_20260608074657</t>
+          <t>ID_20260608074805</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>INC_074657_0.png</t>
+          <t>INC_074805_0.png</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/BOSQUE.xlsx
+++ b/cuadros/JUNIO/BOSQUE.xlsx
@@ -26,12 +26,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor rgb="FF00B0F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +58,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -734,13 +748,12 @@
           <t>OTRAS.</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>SE RECIBEN 1504.10KG DE POLLO ENTERO CONGELADO, EN FACTURA 1499.30KG. DIFERENCIA: 4.8KG EXCEDENTE</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="1" t="n">
         <v>15.31</v>
       </c>
       <c r="K5" t="inlineStr">
@@ -828,7 +841,6 @@
           <t>ID_20260603144429</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -964,7 +976,6 @@
           <t>ID_20260605090644</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1082,7 +1093,7 @@
           <t>SE RECIBEN 13 UNDS DE FLORETES DE BROCOLI, EN FACTURA 15 UNDS. DIFERENCIA: 02 UNDS FALTANTES.</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="2" t="n">
         <v>7.44</v>
       </c>
       <c r="K10" t="inlineStr">
